--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.30-8.13-14-business-continuity-dr/WKBK/90_workbooks/ISMS-IMP-A.5.30.S1_Backup_Inventory_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.30-8.13-14-business-continuity-dr/WKBK/90_workbooks/ISMS-IMP-A.5.30.S1_Backup_Inventory_20260208.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08.02.2026 11:48</t>
+          <t>08.02.2026 12:25</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>08.02.2026 09:48</t>
+          <t>08.02.2026 10:25</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>07.02.2026 15:48</t>
+          <t>07.02.2026 16:25</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>08.02.2026 08:48</t>
+          <t>08.02.2026 09:25</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>06.02.2026 11:48</t>
+          <t>06.02.2026 12:25</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>08.02.2026 11:03</t>
+          <t>08.02.2026 11:40</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>08.02.2026 11:38</t>
+          <t>08.02.2026 12:15</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>07.02.2026 17:48</t>
+          <t>07.02.2026 18:25</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>07.02.2026 11:48</t>
+          <t>07.02.2026 12:25</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
